--- a/mapping/SB_DWH/Mapping_FCT_LOS_WORKSTEP_EVENT.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_LOS_WORKSTEP_EVENT.xlsx
@@ -898,7 +898,11 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr"/>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Ngày dữ liệu</t>
+        </is>
+      </c>
       <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Ngày ảnh chụp (as-of), không phải ngày nghiệp vụ. Là thành phần PK cùng WI_NAME+WORKSTEP_CODE+ENTRYDATE.</t>
@@ -926,7 +930,11 @@
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr"/>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ</t>
+        </is>
+      </c>
       <c r="D18" s="28" t="inlineStr"/>
       <c r="E18" s="29" t="inlineStr">
         <is>
@@ -950,7 +958,11 @@
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr"/>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý</t>
+        </is>
+      </c>
       <c r="D19" s="28" t="inlineStr">
         <is>
           <t>Đã cắt tiền tố hệ nguồn nếu có trong WORKSTEP gốc.</t>
@@ -978,7 +990,11 @@
           <t>TIMESTAMP(18)</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr"/>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Thời điểm vào bước xử lý</t>
+        </is>
+      </c>
       <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Bắt buộc trong khóa vì một hồ sơ có thể quay lại cùng bước nhiều lần.</t>
@@ -1006,7 +1022,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr"/>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>SK bước xử lý</t>
+        </is>
+      </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Lookup DIM_LOS_WORKSTEP theo SYSTEM_CODE+WORKSTEP_CODE và điều kiện hiệu lực thời gian; không khớp = -1.</t>
@@ -1034,7 +1054,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr"/>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>SK quyết định</t>
+        </is>
+      </c>
       <c r="D22" s="28" t="inlineStr">
         <is>
           <t>[CẦN REVIEW] extract/database đánh dấu DECISION_SK là PK, nhưng extract/datamart (dòng Khóa:) chỉ liệt kê PK = DAYID+WI_NAME+WORKSTEP_CODE+ENTRYDATE, không có DECISION_SK/USER_SK — hai nguồn không khớp nhau, cần BA xác nhận. DECISION null/không khớp dùng -1.</t>
@@ -1062,7 +1086,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr"/>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>SK cán bộ xử lý</t>
+        </is>
+      </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
           <t>[CẦN REVIEW] extract/database đánh dấu USER_SK là PK, nhưng extract/datamart (dòng Khóa:) chỉ liệt kê PK = DAYID+WI_NAME+WORKSTEP_CODE+ENTRYDATE, không có DECISION_SK/USER_SK — hai nguồn không khớp nhau, cần BA xác nhận. USERNAME null/không khớp dùng -1.</t>
@@ -1090,7 +1118,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr"/>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>SK hồ sơ</t>
+        </is>
+      </c>
       <c r="D24" s="28" t="inlineStr">
         <is>
           <t>[CẦN REVIEW] Mô tả nguồn chỉ ghi "KỸ THUẬT — Khóa tới DIM_LOS_APPLICATION", không nêu cột khóa lookup cụ thể (WI_NAME?) hay điều kiện hiệu lực thời gian — công thức dưới đây là suy đoán dựa trên khóa nghiệp vụ WI_NAME, cần BA/DEV xác nhận.</t>
@@ -1118,7 +1150,11 @@
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr"/>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Hệ nguồn</t>
+        </is>
+      </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
           <t>Gán theo tuyến bảng nguồn/STG_LOS, không phải hậu tố WI_NAME (chỉ dùng để kiểm tra chất lượng).</t>
@@ -1146,7 +1182,11 @@
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr"/>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>Thời điểm ra khỏi bước xử lý</t>
+        </is>
+      </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
           <t>NULL nghĩa là hồ sơ đang nằm tại bước này.</t>
@@ -1174,7 +1214,11 @@
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr"/>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Mã quyết định</t>
+        </is>
+      </c>
       <c r="D27" s="28" t="inlineStr"/>
       <c r="E27" s="29" t="inlineStr">
         <is>
@@ -1198,7 +1242,11 @@
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr"/>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Tài khoản cán bộ xử lý</t>
+        </is>
+      </c>
       <c r="D28" s="28" t="inlineStr"/>
       <c r="E28" s="29" t="inlineStr">
         <is>
@@ -1222,7 +1270,11 @@
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr"/>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
       <c r="D29" s="28" t="inlineStr"/>
       <c r="E29" s="29" t="inlineStr">
         <is>
@@ -1246,7 +1298,11 @@
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr"/>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>Mã lý do hủy hồ sơ</t>
+        </is>
+      </c>
       <c r="D30" s="28" t="inlineStr">
         <is>
           <t>Chỉ có nguồn RLOS (lý do ĐVKD hủy hồ sơ); CLOS không phát sinh cột này.</t>
@@ -1274,7 +1330,11 @@
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C31" s="27" t="inlineStr"/>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>Diễn giải lý do hủy hồ sơ</t>
+        </is>
+      </c>
       <c r="D31" s="28" t="inlineStr">
         <is>
           <t>Chỉ có nguồn RLOS, lấy từ NG_SB_RLOS_MAS_REASON; CLOS không phát sinh cột này.</t>
@@ -1302,7 +1362,11 @@
           <t>NUMBER(12)</t>
         </is>
       </c>
-      <c r="C32" s="27" t="inlineStr"/>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo hệ nguồn (giây)</t>
+        </is>
+      </c>
       <c r="D32" s="28" t="inlineStr">
         <is>
           <t>Đơn vị GIÂY theo xác nhận BA. Giữ lại để đối soát với ba cột TAT_*_HOUR tính lại bên dưới.</t>
@@ -1330,7 +1394,11 @@
           <t>NUMBER(18,6)</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr"/>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo lịch tự nhiên (giờ)</t>
+        </is>
+      </c>
       <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Đơn vị GIỜ, theo lịch tự nhiên (không trừ ngày nghỉ). Event chưa có EXITDATE thì NULL.</t>
@@ -1358,7 +1426,11 @@
           <t>NUMBER(18,6)</t>
         </is>
       </c>
-      <c r="C34" s="27" t="inlineStr"/>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo giờ làm việc (giờ)</t>
+        </is>
+      </c>
       <c r="D34" s="28" t="inlineStr">
         <is>
           <t>Đơn vị GIỜ, loại trừ ngày lễ/chiều Thứ Bảy/Chủ Nhật, tính giờ 8-12 và 13-17. Event chưa có EXITDATE thì NULL.</t>
@@ -1386,7 +1458,11 @@
           <t>NUMBER(18,6)</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr"/>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo SLA (giờ)</t>
+        </is>
+      </c>
       <c r="D35" s="28" t="inlineStr">
         <is>
           <t>Đơn vị GIỜ, theo cam kết SLA, tính giờ 8-11:30 và 13:30-16:30. Event chưa có EXITDATE thì NULL.</t>
@@ -1414,7 +1490,11 @@
           <t>NUMBER(5)</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr"/>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>Thứ tự sự kiện (cũ đến mới)</t>
+        </is>
+      </c>
       <c r="D36" s="28" t="inlineStr">
         <is>
           <t>Dùng để xác định sự kiện trả về đầu tiên (BC7.FIRST_WORKSTEP_RETURN).</t>
@@ -1442,7 +1522,11 @@
           <t>NUMBER(5)</t>
         </is>
       </c>
-      <c r="C37" s="27" t="inlineStr"/>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>Thứ tự sự kiện (mới đến cũ)</t>
+        </is>
+      </c>
       <c r="D37" s="28" t="inlineStr">
         <is>
           <t>Thứ tự logical event mới-&gt;cũ sau khi loại trùng phiên bản ngày: tại DAYID phân tích D, trước hết lấy phiên bản DAYID lớn nhất &lt;=D cho mỗi (WI_NAME,WORKSTEP_CODE,ENTRYDATE), sau đó xếp theo ENTRYDATE DESC. Không xếp trực tiếp trên các version rows.</t>
@@ -1470,7 +1554,11 @@
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr"/>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Lần phê duyệt đầu/lại</t>
+        </is>
+      </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
           <t>Trường BI_FLAG_APPROVAL của BC5.</t>
@@ -1498,7 +1586,11 @@
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C39" s="27" t="inlineStr"/>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>Bước xử lý liền trước</t>
+        </is>
+      </c>
       <c r="D39" s="28" t="inlineStr"/>
       <c r="E39" s="29" t="inlineStr">
         <is>
